--- a/data/trans_bre/P6901-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6901-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,65; 21,88</t>
+          <t>-22,28; 19,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 30,41</t>
+          <t>-13,44; 30,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 30,09</t>
+          <t>-9,74; 30,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 33,43</t>
+          <t>-23,05; 37,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-29,96; 34,08</t>
+          <t>-27,86; 31,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 54,89</t>
+          <t>-17,9; 55,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 61,58</t>
+          <t>-14,6; 59,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,05; 72,46</t>
+          <t>-27,56; 80,84</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 20,3</t>
+          <t>-11,71; 20,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 4,91</t>
+          <t>-27,29; 5,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 9,8</t>
+          <t>-15,12; 8,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 22,99</t>
+          <t>-8,44; 20,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 28,25</t>
+          <t>-13,18; 27,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,44; 5,4</t>
+          <t>-30,17; 5,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 11,17</t>
+          <t>-16,31; 10,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 32,22</t>
+          <t>-9,12; 28,88</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-37,35; 11,94</t>
+          <t>-30,09; 13,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 9,11</t>
+          <t>-35,96; 10,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 24,4</t>
+          <t>-22,57; 24,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 30,73</t>
+          <t>-4,75; 30,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,47; 16,76</t>
+          <t>-36,32; 18,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-40,58; 10,66</t>
+          <t>-38,33; 13,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 34,74</t>
+          <t>-26,58; 33,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 70,08</t>
+          <t>-7,32; 66,33</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 21,61</t>
+          <t>-20,67; 21,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,24; 10,11</t>
+          <t>-29,89; 9,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 23,17</t>
+          <t>-16,89; 22,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 44,88</t>
+          <t>-3,72; 45,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 33,88</t>
+          <t>-27,18; 33,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,33; 12,72</t>
+          <t>-33,61; 11,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 33,49</t>
+          <t>-19,02; 34,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 99,95</t>
+          <t>-6,48; 90,19</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-41,56; 34,8</t>
+          <t>-44,63; 35,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-25,41; 39,4</t>
+          <t>-26,6; 34,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-39,34; 32,41</t>
+          <t>-41,02; 29,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 19,09</t>
+          <t>-19,75; 22,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-55,99; 62,66</t>
+          <t>-58,25; 60,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,48; 73,21</t>
+          <t>-29,68; 61,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 49,31</t>
+          <t>-46,1; 43,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 26,26</t>
+          <t>-21,32; 31,44</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,16; 24,39</t>
+          <t>-31,63; 23,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 30,62</t>
+          <t>-13,61; 29,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30,53; 70,6</t>
+          <t>30,68; 70,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,59; 25,02</t>
+          <t>-13,9; 26,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 35,74</t>
+          <t>-37,13; 33,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 49,34</t>
+          <t>-14,63; 47,24</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,89; 239,85</t>
+          <t>44,24; 240,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 45,61</t>
+          <t>-18,54; 47,72</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 31,45</t>
+          <t>0,83; 31,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 39,93</t>
+          <t>1,14; 41,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 20,91</t>
+          <t>-2,89; 20,66</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 20,69</t>
+          <t>-9,81; 21,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,11; 53,15</t>
+          <t>2,47; 53,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,96; 106,17</t>
+          <t>2,6; 115,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 28,35</t>
+          <t>-2,93; 28,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 35,12</t>
+          <t>-12,98; 36,95</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 9,3</t>
+          <t>-19,39; 9,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 30,56</t>
+          <t>-7,8; 31,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,84; 56,8</t>
+          <t>7,32; 54,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-41,88; -2,91</t>
+          <t>-45,61; -4,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 12,62</t>
+          <t>-23,18; 12,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 53,02</t>
+          <t>-9,26; 54,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,85; 163,33</t>
+          <t>15,2; 165,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,7; -3,58</t>
+          <t>-48,02; -5,56</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 9,7</t>
+          <t>-3,94; 9,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 11,08</t>
+          <t>-3,46; 10,73</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,77; 16,95</t>
+          <t>3,66; 17,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 13,76</t>
+          <t>-3,01; 13,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 13,49</t>
+          <t>-5,03; 13,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 15,56</t>
+          <t>-4,45; 15,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 24,51</t>
+          <t>4,84; 24,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 20,14</t>
+          <t>-3,74; 18,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6901-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6901-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,45</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,28; 19,62</t>
+          <t>-27,5; 18,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 30,56</t>
+          <t>-15,06; 28,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 30,01</t>
+          <t>-12,17; 29,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 37,2</t>
+          <t>-25,48; 25,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 31,1</t>
+          <t>-34,23; 30,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,9; 55,82</t>
+          <t>-18,02; 50,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 59,93</t>
+          <t>-17,01; 60,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-27,56; 80,84</t>
+          <t>-30,82; 46,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,7</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 20,21</t>
+          <t>-10,12; 19,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 5,21</t>
+          <t>-29,02; 4,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 8,92</t>
+          <t>-15,37; 7,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 20,76</t>
+          <t>-9,68; 19,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 27,72</t>
+          <t>-11,09; 26,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,17; 5,6</t>
+          <t>-31,9; 5,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 10,03</t>
+          <t>-16,06; 8,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 28,88</t>
+          <t>-10,49; 27,0</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,52</t>
+          <t>11,8</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 13,34</t>
+          <t>-34,95; 11,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 10,52</t>
+          <t>-36,51; 9,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,57; 24,52</t>
+          <t>-25,22; 24,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 30,95</t>
+          <t>-5,6; 28,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,32; 18,73</t>
+          <t>-41,82; 15,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-38,33; 13,62</t>
+          <t>-40,06; 11,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-26,58; 33,67</t>
+          <t>-27,93; 33,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 66,33</t>
+          <t>-8,39; 63,41</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,95</t>
+          <t>3,01</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>4,2%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 21,47</t>
+          <t>-20,07; 20,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,89; 9,68</t>
+          <t>-29,87; 9,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 22,52</t>
+          <t>-17,17; 21,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 45,88</t>
+          <t>-14,95; 23,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,18; 33,0</t>
+          <t>-25,69; 32,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 11,72</t>
+          <t>-34,26; 11,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,02; 34,0</t>
+          <t>-18,79; 31,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 90,19</t>
+          <t>-18,08; 42,54</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>-1,55%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-44,63; 35,25</t>
+          <t>-45,7; 38,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,6; 34,87</t>
+          <t>-23,33; 37,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,02; 29,09</t>
+          <t>-44,46; 31,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 22,33</t>
+          <t>-20,65; 19,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-58,25; 60,26</t>
+          <t>-58,07; 67,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-29,68; 61,49</t>
+          <t>-27,33; 67,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-46,1; 43,39</t>
+          <t>-47,4; 46,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 31,44</t>
+          <t>-22,97; 25,65</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,76</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 23,43</t>
+          <t>-30,01; 25,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 29,76</t>
+          <t>-13,0; 29,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30,68; 70,61</t>
+          <t>29,13; 72,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 26,48</t>
+          <t>-15,14; 23,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,13; 33,26</t>
+          <t>-36,48; 36,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 47,24</t>
+          <t>-15,69; 45,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44,24; 240,06</t>
+          <t>41,07; 270,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 47,72</t>
+          <t>-18,93; 41,3</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>6,67</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,83; 31,78</t>
+          <t>4,04; 31,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 41,24</t>
+          <t>2,13; 40,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 20,66</t>
+          <t>-4,18; 20,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 21,21</t>
+          <t>-7,01; 21,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 53,66</t>
+          <t>5,81; 55,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 115,26</t>
+          <t>3,9; 106,9</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 28,72</t>
+          <t>-4,52; 28,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 36,95</t>
+          <t>-8,52; 35,39</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-17,65</t>
+          <t>-10,09</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-19,34%</t>
+          <t>-11,0%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 9,74</t>
+          <t>-18,58; 10,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 31,95</t>
+          <t>-9,41; 31,1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,32; 54,87</t>
+          <t>7,53; 56,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-45,61; -4,7</t>
+          <t>-23,2; 2,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 12,98</t>
+          <t>-22,33; 14,16</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 54,1</t>
+          <t>-10,98; 52,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,2; 165,6</t>
+          <t>16,92; 164,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,02; -5,56</t>
+          <t>-24,61; 2,3</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 9,67</t>
+          <t>-3,69; 9,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 10,73</t>
+          <t>-4,49; 11,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,66; 17,31</t>
+          <t>3,19; 17,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 13,01</t>
+          <t>-3,92; 8,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 13,3</t>
+          <t>-4,71; 13,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 15,32</t>
+          <t>-6,04; 16,14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,84; 24,41</t>
+          <t>3,99; 24,91</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 18,93</t>
+          <t>-5,08; 12,12</t>
         </is>
       </c>
     </row>
